--- a/table_config/_tables/__tables__.xlsx
+++ b/table_config/_tables/__tables__.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11775"/>
+    <workbookView windowWidth="26040" windowHeight="11850"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="44">
   <si>
     <t>##var</t>
   </si>
@@ -123,6 +123,42 @@
   </si>
   <si>
     <t>one</t>
+  </si>
+  <si>
+    <t>Character.LvData</t>
+  </si>
+  <si>
+    <t>TbLvData</t>
+  </si>
+  <si>
+    <t>Character/LvData-等级-01.xlsx</t>
+  </si>
+  <si>
+    <t>id,lv</t>
+  </si>
+  <si>
+    <t>Character.ClassData</t>
+  </si>
+  <si>
+    <t>TbClassData</t>
+  </si>
+  <si>
+    <t>Character/ClassData-职业-02.xlsx</t>
+  </si>
+  <si>
+    <t>id,type</t>
+  </si>
+  <si>
+    <t>Character.BaseEquipmentData</t>
+  </si>
+  <si>
+    <t>TbBaseEquipmentData</t>
+  </si>
+  <si>
+    <t>Character/BaseWeaponData-装备-03.xlsx</t>
+  </si>
+  <si>
+    <t>id,base_type</t>
   </si>
 </sst>
 </file>
@@ -1104,24 +1140,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:L14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="6.45833333333333" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9.54166666666667" style="1" customWidth="1"/>
-    <col min="3" max="3" width="27.0916666666667" style="1" customWidth="1"/>
-    <col min="4" max="4" width="18.725" style="1" customWidth="1"/>
-    <col min="5" max="5" width="22.275" style="1" customWidth="1"/>
-    <col min="6" max="6" width="67.275" style="1" customWidth="1"/>
-    <col min="7" max="7" width="34.625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="6.45454545454545" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.54545454545454" style="1" customWidth="1"/>
+    <col min="3" max="3" width="27.0909090909091" style="1" customWidth="1"/>
+    <col min="4" max="4" width="18.7272727272727" style="1" customWidth="1"/>
+    <col min="5" max="5" width="22.2727272727273" style="1" customWidth="1"/>
+    <col min="6" max="6" width="67.2727272727273" style="1" customWidth="1"/>
+    <col min="7" max="7" width="34.6272727272727" style="1" customWidth="1"/>
     <col min="8" max="8" width="9" style="1" customWidth="1"/>
-    <col min="9" max="9" width="31.3666666666667" style="1" customWidth="1"/>
-    <col min="10" max="10" width="9.81666666666667" style="1" customWidth="1"/>
-    <col min="11" max="11" width="5.18333333333333" style="1" customWidth="1"/>
-    <col min="12" max="12" width="11.8166666666667" style="1" customWidth="1"/>
+    <col min="9" max="9" width="31.3636363636364" style="1" customWidth="1"/>
+    <col min="10" max="10" width="9.81818181818182" style="1" customWidth="1"/>
+    <col min="11" max="11" width="5.18181818181818" style="1" customWidth="1"/>
+    <col min="12" max="12" width="11.8181818181818" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25" spans="1:12">
+    <row r="1" spans="1:12">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1159,7 +1195,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" ht="14.25" spans="1:12">
+    <row r="2" spans="1:12">
       <c r="A2" s="2" t="s">
         <v>12</v>
       </c>
@@ -1193,7 +1229,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" ht="71.25" spans="1:12">
+    <row r="3" ht="70" spans="1:12">
       <c r="A3" s="4" t="s">
         <v>12</v>
       </c>
@@ -1221,7 +1257,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" ht="14.25" spans="1:12">
+    <row r="4" spans="1:12">
       <c r="A4" s="6"/>
       <c r="B4" s="6"/>
       <c r="C4" s="6" t="s">
@@ -1245,7 +1281,7 @@
       <c r="K4" s="8"/>
       <c r="L4" s="8"/>
     </row>
-    <row r="5" ht="14.25" spans="1:12">
+    <row r="5" spans="1:12">
       <c r="A5" s="6"/>
       <c r="B5" s="6"/>
       <c r="C5" s="6"/>
@@ -1259,49 +1295,79 @@
       <c r="K5" s="8"/>
       <c r="L5" s="8"/>
     </row>
-    <row r="6" ht="14.25" spans="1:12">
+    <row r="6" spans="1:12">
       <c r="A6" s="6"/>
       <c r="B6" s="6"/>
-      <c r="C6" s="6"/>
-      <c r="D6" s="6"/>
-      <c r="E6" s="6"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="6"/>
+      <c r="C6" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="E6" s="6">
+        <v>1</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>35</v>
+      </c>
       <c r="H6" s="6"/>
       <c r="I6" s="6"/>
       <c r="J6" s="8"/>
       <c r="K6" s="8"/>
       <c r="L6" s="8"/>
     </row>
-    <row r="7" ht="14.25" spans="1:12">
+    <row r="7" spans="1:12">
       <c r="A7" s="6"/>
       <c r="B7" s="6"/>
-      <c r="C7" s="6"/>
-      <c r="D7" s="6"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="6"/>
+      <c r="C7" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="E7" s="6">
+        <v>1</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>39</v>
+      </c>
       <c r="H7" s="6"/>
       <c r="I7" s="6"/>
       <c r="J7" s="8"/>
       <c r="K7" s="8"/>
       <c r="L7" s="8"/>
     </row>
-    <row r="8" ht="14.25" spans="1:12">
+    <row r="8" spans="1:12">
       <c r="A8" s="6"/>
       <c r="B8" s="6"/>
-      <c r="C8" s="6"/>
-      <c r="D8" s="6"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="6"/>
+      <c r="C8" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="E8" s="6">
+        <v>1</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>43</v>
+      </c>
       <c r="H8" s="6"/>
       <c r="I8" s="6"/>
       <c r="J8" s="8"/>
       <c r="K8" s="8"/>
       <c r="L8" s="8"/>
     </row>
-    <row r="9" ht="14.25" spans="1:12">
+    <row r="9" spans="1:12">
       <c r="A9" s="6"/>
       <c r="B9" s="6"/>
       <c r="C9" s="6"/>
@@ -1315,7 +1381,7 @@
       <c r="K9" s="8"/>
       <c r="L9" s="8"/>
     </row>
-    <row r="10" ht="14.25" spans="1:12">
+    <row r="10" spans="1:12">
       <c r="A10" s="6"/>
       <c r="B10" s="6"/>
       <c r="C10" s="6"/>
@@ -1329,7 +1395,7 @@
       <c r="K10" s="8"/>
       <c r="L10" s="8"/>
     </row>
-    <row r="11" ht="14.25" spans="1:12">
+    <row r="11" spans="1:12">
       <c r="A11" s="6"/>
       <c r="B11" s="6"/>
       <c r="C11" s="6"/>
@@ -1343,34 +1409,48 @@
       <c r="K11" s="8"/>
       <c r="L11" s="8"/>
     </row>
-    <row r="12" ht="14.25" spans="1:12">
+    <row r="12" spans="1:12">
       <c r="A12" s="6"/>
       <c r="B12" s="6"/>
       <c r="C12" s="6"/>
       <c r="D12" s="6"/>
       <c r="E12" s="6"/>
-      <c r="F12" s="7"/>
-      <c r="G12" s="10"/>
+      <c r="F12" s="9"/>
+      <c r="G12" s="6"/>
       <c r="H12" s="6"/>
       <c r="I12" s="6"/>
       <c r="J12" s="8"/>
       <c r="K12" s="8"/>
       <c r="L12" s="8"/>
     </row>
-    <row r="13" ht="14.25" spans="1:12">
+    <row r="13" spans="1:12">
       <c r="A13" s="6"/>
       <c r="B13" s="6"/>
       <c r="C13" s="6"/>
       <c r="D13" s="6"/>
       <c r="E13" s="6"/>
       <c r="F13" s="7"/>
-      <c r="G13" s="2"/>
+      <c r="G13" s="10"/>
       <c r="H13" s="6"/>
       <c r="I13" s="6"/>
       <c r="J13" s="8"/>
       <c r="K13" s="8"/>
       <c r="L13" s="8"/>
     </row>
+    <row r="14" spans="1:12">
+      <c r="A14" s="6"/>
+      <c r="B14" s="6"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="7"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="6"/>
+      <c r="I14" s="6"/>
+      <c r="J14" s="8"/>
+      <c r="K14" s="8"/>
+      <c r="L14" s="8"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
